--- a/docs/光和稼働データ収集装置デバイスマップ.xlsx
+++ b/docs/光和稼働データ収集装置デバイスマップ.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myProgram\GitHub\ForMitsuwa\factory_visualize_server_atmw\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB67241-87C3-4473-86AA-91543A1E1618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877E1234-4109-4527-BC61-341CBBEEFEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{2B542973-F752-4A81-A420-BFC37E5D0A51}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{2B542973-F752-4A81-A420-BFC37E5D0A51}"/>
   </bookViews>
   <sheets>
     <sheet name="旧割付" sheetId="1" r:id="rId1"/>
-    <sheet name="20260622" sheetId="2" r:id="rId2"/>
+    <sheet name="20261017" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -23,6 +23,136 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>user</author>
+  </authors>
+  <commentList>
+    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{DD7276A9-1BA8-4376-A68B-8B46A03145DC}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">タッチパネルデータでは
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="2"/>
+            <charset val="128"/>
+          </rPr>
+          <t>DM436</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">を使用している
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="2"/>
+            <charset val="128"/>
+          </rPr>
+          <t>(規則性が崩れている)</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+生産数実績</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="2"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">=DM536
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>生産数目標</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="2"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">=DM636
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>アラーム数</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="2"/>
+            <charset val="128"/>
+          </rPr>
+          <t>=DM736</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2137,10 +2267,6 @@
     <t>DM449</t>
   </si>
   <si>
-    <t>36号機</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>46号機</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2560,12 +2686,19 @@
   <si>
     <t>ZF90003</t>
   </si>
+  <si>
+    <t>36号機</t>
+    <rPh sb="2" eb="4">
+      <t>ゴウキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2623,8 +2756,22 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="MS P ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2676,6 +2823,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF66CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2792,7 +2945,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2842,9 +2995,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF99CC"/>
       <color rgb="FF24D642"/>
       <color rgb="FFFF66CC"/>
-      <color rgb="FFFF99CC"/>
       <color rgb="FF0000FF"/>
     </mruColors>
   </colors>
@@ -3286,13 +3439,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62123ED-9C66-404D-AD1C-3CC6E3D9A234}">
   <dimension ref="B1:AZ32"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
     <col min="3" max="52" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:52">
       <c r="B1" t="s">
         <v>570</v>
       </c>
@@ -3447,7 +3600,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="2" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:52">
       <c r="B2" s="4" t="s">
         <v>38</v>
       </c>
@@ -3602,7 +3755,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="3" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:52">
       <c r="B3" s="4" t="s">
         <v>66</v>
       </c>
@@ -3743,7 +3896,7 @@
       <c r="AY3" s="10"/>
       <c r="AZ3" s="10"/>
     </row>
-    <row r="4" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:52">
       <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
@@ -3898,7 +4051,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:52">
       <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
@@ -4053,7 +4206,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:52">
       <c r="B6" s="1" t="s">
         <v>24</v>
       </c>
@@ -4208,12 +4361,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:52">
       <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:52">
       <c r="B9" s="2" t="s">
         <v>52</v>
       </c>
@@ -4368,7 +4521,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="10" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:52">
       <c r="B10" s="1"/>
       <c r="C10" t="s">
         <v>3</v>
@@ -4521,7 +4674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:52">
       <c r="B11" s="2"/>
       <c r="C11" t="s">
         <v>43</v>
@@ -4674,10 +4827,10 @@
         <v>335</v>
       </c>
     </row>
-    <row r="12" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:52">
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:52">
       <c r="B13" s="2">
         <v>0.16666666666666666</v>
       </c>
@@ -4832,7 +4985,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="14" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:52">
       <c r="B14" s="1" t="s">
         <v>3</v>
       </c>
@@ -4987,7 +5140,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:52">
       <c r="B15" s="2">
         <v>0.99930555555555556</v>
       </c>
@@ -5142,7 +5295,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="16" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:52">
       <c r="B16" s="2">
         <v>0</v>
       </c>
@@ -5297,7 +5450,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="17" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:52">
       <c r="B17" s="1" t="s">
         <v>3</v>
       </c>
@@ -5452,7 +5605,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:52">
       <c r="B18" s="2">
         <v>0.16597222222222222</v>
       </c>
@@ -5607,14 +5760,14 @@
         <v>423</v>
       </c>
     </row>
-    <row r="20" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:52">
       <c r="B20" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="14"/>
     </row>
-    <row r="21" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:52">
       <c r="B21" s="11" t="s">
         <v>55</v>
       </c>
@@ -5625,7 +5778,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="22" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:52">
       <c r="B22" s="11" t="s">
         <v>56</v>
       </c>
@@ -5636,7 +5789,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="23" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:52">
       <c r="B23" s="7" t="s">
         <v>57</v>
       </c>
@@ -5647,7 +5800,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="24" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:52">
       <c r="B24" s="7" t="s">
         <v>58</v>
       </c>
@@ -5658,7 +5811,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="25" spans="2:52" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:52">
       <c r="B25" s="7" t="s">
         <v>59</v>
       </c>
@@ -5669,7 +5822,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="26" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:52" s="5" customFormat="1">
       <c r="B26" s="8" t="s">
         <v>60</v>
       </c>
@@ -5680,7 +5833,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="27" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:52" s="5" customFormat="1">
       <c r="B27" s="12" t="s">
         <v>61</v>
       </c>
@@ -5691,7 +5844,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="28" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:52" s="5" customFormat="1">
       <c r="B28" s="8" t="s">
         <v>62</v>
       </c>
@@ -5702,23 +5855,23 @@
         <v>567</v>
       </c>
     </row>
-    <row r="29" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:52" s="5" customFormat="1">
       <c r="B29" t="s">
         <v>39</v>
       </c>
       <c r="C29" s="6"/>
     </row>
-    <row r="30" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:52" s="5" customFormat="1">
       <c r="B30" t="s">
         <v>25</v>
       </c>
       <c r="C30" s="6"/>
     </row>
-    <row r="31" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:52" s="5" customFormat="1">
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
     </row>
-    <row r="32" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:52" s="5" customFormat="1">
       <c r="B32" s="6" t="s">
         <v>63</v>
       </c>
@@ -5735,15 +5888,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65309343-5134-42B2-91CD-0F008F8E70CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65309343-5134-42B2-91CD-0F008F8E70CA}">
   <dimension ref="B1:BK32"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
     <col min="3" max="52" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:63">
       <c r="B1" s="22" t="s">
         <v>570</v>
       </c>
@@ -5825,7 +5978,7 @@
       <c r="AB1" t="s">
         <v>594</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="23" t="s">
         <v>595</v>
       </c>
       <c r="AD1" t="s">
@@ -5898,40 +6051,40 @@
         <v>618</v>
       </c>
       <c r="BA1" t="s">
+        <v>640</v>
+      </c>
+      <c r="BB1" t="s">
         <v>641</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>642</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>643</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>644</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>645</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>646</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>647</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>648</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>649</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>650</v>
       </c>
-      <c r="BK1" t="s">
-        <v>651</v>
-      </c>
     </row>
-    <row r="2" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:63">
       <c r="B2" s="4" t="s">
         <v>38</v>
       </c>
@@ -6086,40 +6239,40 @@
         <v>247</v>
       </c>
       <c r="BA2" t="s">
+        <v>629</v>
+      </c>
+      <c r="BB2" t="s">
         <v>630</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>631</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>632</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>633</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>634</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>635</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>636</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>637</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>638</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>639</v>
       </c>
-      <c r="BK2" t="s">
-        <v>640</v>
-      </c>
     </row>
-    <row r="3" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:63">
       <c r="B3" s="4" t="s">
         <v>66</v>
       </c>
@@ -6190,7 +6343,7 @@
         <v>539</v>
       </c>
       <c r="Y3" s="21" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="Z3" s="21" t="s">
         <v>561</v>
@@ -6202,19 +6355,19 @@
         <v>543</v>
       </c>
       <c r="AC3" s="21" t="s">
-        <v>561</v>
+        <v>752</v>
       </c>
       <c r="AD3" s="21" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AE3" s="21" t="s">
         <v>561</v>
       </c>
       <c r="AF3" s="21" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AG3" s="21" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AH3" s="10" t="s">
         <v>549</v>
@@ -6229,22 +6382,22 @@
         <v>551</v>
       </c>
       <c r="AL3" s="10" t="s">
+        <v>619</v>
+      </c>
+      <c r="AM3" s="21" t="s">
+        <v>561</v>
+      </c>
+      <c r="AN3" s="10" t="s">
         <v>620</v>
       </c>
-      <c r="AM3" s="21" t="s">
-        <v>619</v>
-      </c>
-      <c r="AN3" s="10" t="s">
+      <c r="AO3" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="AO3" s="10" t="s">
+      <c r="AP3" s="10" t="s">
         <v>622</v>
       </c>
-      <c r="AP3" s="10" t="s">
+      <c r="AQ3" s="10" t="s">
         <v>623</v>
-      </c>
-      <c r="AQ3" s="10" t="s">
-        <v>624</v>
       </c>
       <c r="AR3" s="10" t="s">
         <v>559</v>
@@ -6253,7 +6406,7 @@
         <v>560</v>
       </c>
       <c r="AT3" s="21" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AU3" s="13" t="s">
         <v>561</v>
@@ -6271,7 +6424,7 @@
         <v>561</v>
       </c>
       <c r="AZ3" s="21" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="BA3" s="13" t="s">
         <v>561</v>
@@ -6283,7 +6436,7 @@
         <v>561</v>
       </c>
       <c r="BD3" s="21" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="BE3" s="13" t="s">
         <v>561</v>
@@ -6307,888 +6460,764 @@
         <v>561</v>
       </c>
     </row>
-    <row r="4" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:63">
       <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="23" t="s">
+      <c r="H4" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" t="s">
         <v>110</v>
       </c>
-      <c r="J4" s="23" t="s">
+      <c r="J4" t="s">
         <v>113</v>
       </c>
-      <c r="K4" s="23" t="s">
+      <c r="K4" t="s">
         <v>116</v>
       </c>
-      <c r="L4" s="23" t="s">
+      <c r="L4" t="s">
         <v>117</v>
       </c>
-      <c r="M4" s="23" t="s">
+      <c r="M4" t="s">
         <v>118</v>
       </c>
-      <c r="N4" s="23" t="s">
+      <c r="N4" t="s">
         <v>119</v>
       </c>
-      <c r="O4" s="23" t="s">
+      <c r="O4" t="s">
         <v>120</v>
       </c>
-      <c r="P4" s="23" t="s">
+      <c r="P4" t="s">
         <v>121</v>
       </c>
-      <c r="Q4" s="23" t="s">
+      <c r="Q4" t="s">
         <v>122</v>
       </c>
-      <c r="R4" s="23" t="s">
+      <c r="R4" t="s">
         <v>123</v>
       </c>
-      <c r="S4" s="23" t="s">
+      <c r="S4" t="s">
         <v>124</v>
       </c>
-      <c r="T4" s="23" t="s">
+      <c r="T4" t="s">
         <v>125</v>
       </c>
-      <c r="U4" s="23" t="s">
+      <c r="U4" t="s">
         <v>126</v>
       </c>
-      <c r="V4" s="23" t="s">
+      <c r="V4" t="s">
         <v>127</v>
       </c>
-      <c r="W4" s="23" t="s">
+      <c r="W4" t="s">
         <v>128</v>
       </c>
-      <c r="X4" s="23" t="s">
+      <c r="X4" t="s">
         <v>129</v>
       </c>
-      <c r="Y4" s="23" t="s">
+      <c r="Y4" t="s">
         <v>130</v>
       </c>
-      <c r="Z4" s="23" t="s">
+      <c r="Z4" t="s">
         <v>131</v>
       </c>
-      <c r="AA4" s="23" t="s">
+      <c r="AA4" t="s">
         <v>132</v>
       </c>
-      <c r="AB4" s="23" t="s">
+      <c r="AB4" t="s">
         <v>133</v>
       </c>
-      <c r="AC4" s="23" t="s">
+      <c r="AC4" t="s">
         <v>134</v>
       </c>
-      <c r="AD4" s="23" t="s">
+      <c r="AD4" t="s">
         <v>135</v>
       </c>
-      <c r="AE4" s="23" t="s">
+      <c r="AE4" t="s">
         <v>136</v>
       </c>
-      <c r="AF4" s="23" t="s">
+      <c r="AF4" t="s">
         <v>137</v>
       </c>
-      <c r="AG4" s="23" t="s">
+      <c r="AG4" t="s">
         <v>138</v>
       </c>
-      <c r="AH4" s="23" t="s">
+      <c r="AH4" t="s">
         <v>139</v>
       </c>
-      <c r="AI4" s="23" t="s">
+      <c r="AI4" t="s">
         <v>140</v>
       </c>
-      <c r="AJ4" s="23" t="s">
+      <c r="AJ4" t="s">
         <v>141</v>
       </c>
-      <c r="AK4" s="23" t="s">
+      <c r="AK4" t="s">
         <v>142</v>
       </c>
-      <c r="AL4" s="23" t="s">
+      <c r="AL4" t="s">
         <v>143</v>
       </c>
-      <c r="AM4" s="23" t="s">
+      <c r="AM4" t="s">
         <v>144</v>
       </c>
-      <c r="AN4" s="23" t="s">
+      <c r="AN4" t="s">
         <v>145</v>
       </c>
-      <c r="AO4" s="23" t="s">
+      <c r="AO4" t="s">
         <v>146</v>
       </c>
-      <c r="AP4" s="23" t="s">
+      <c r="AP4" t="s">
         <v>147</v>
       </c>
-      <c r="AQ4" s="23" t="s">
+      <c r="AQ4" t="s">
         <v>148</v>
       </c>
-      <c r="AR4" s="23" t="s">
+      <c r="AR4" t="s">
         <v>223</v>
       </c>
-      <c r="AS4" s="23" t="s">
+      <c r="AS4" t="s">
         <v>224</v>
       </c>
-      <c r="AT4" s="23" t="s">
+      <c r="AT4" t="s">
         <v>225</v>
       </c>
-      <c r="AU4" s="23" t="s">
+      <c r="AU4" t="s">
         <v>226</v>
       </c>
-      <c r="AV4" s="23" t="s">
+      <c r="AV4" t="s">
         <v>227</v>
       </c>
-      <c r="AW4" s="23" t="s">
+      <c r="AW4" t="s">
         <v>228</v>
       </c>
-      <c r="AX4" s="23" t="s">
+      <c r="AX4" t="s">
         <v>229</v>
       </c>
-      <c r="AY4" s="23" t="s">
+      <c r="AY4" t="s">
         <v>230</v>
       </c>
-      <c r="AZ4" s="23" t="s">
+      <c r="AZ4" t="s">
         <v>21</v>
       </c>
-      <c r="BA4" s="23" t="s">
+      <c r="BA4" t="s">
+        <v>719</v>
+      </c>
+      <c r="BB4" t="s">
         <v>720</v>
       </c>
-      <c r="BB4" s="23" t="s">
+      <c r="BC4" t="s">
         <v>721</v>
       </c>
-      <c r="BC4" s="23" t="s">
+      <c r="BD4" t="s">
         <v>722</v>
       </c>
-      <c r="BD4" s="23" t="s">
+      <c r="BE4" t="s">
         <v>723</v>
       </c>
-      <c r="BE4" s="23" t="s">
+      <c r="BF4" t="s">
         <v>724</v>
       </c>
-      <c r="BF4" s="23" t="s">
+      <c r="BG4" t="s">
         <v>725</v>
       </c>
-      <c r="BG4" s="23" t="s">
+      <c r="BH4" t="s">
         <v>726</v>
       </c>
-      <c r="BH4" s="23" t="s">
+      <c r="BI4" t="s">
         <v>727</v>
       </c>
-      <c r="BI4" s="23" t="s">
+      <c r="BJ4" t="s">
         <v>728</v>
       </c>
-      <c r="BJ4" s="23" t="s">
+      <c r="BK4" t="s">
         <v>729</v>
       </c>
-      <c r="BK4" s="23" t="s">
-        <v>730</v>
-      </c>
     </row>
-    <row r="5" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:63">
       <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="23" t="s">
+      <c r="H5" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" t="s">
         <v>111</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="J5" t="s">
         <v>114</v>
       </c>
-      <c r="K5" s="23" t="s">
+      <c r="K5" t="s">
         <v>149</v>
       </c>
-      <c r="L5" s="23" t="s">
+      <c r="L5" t="s">
         <v>150</v>
       </c>
-      <c r="M5" s="23" t="s">
+      <c r="M5" t="s">
         <v>151</v>
       </c>
-      <c r="N5" s="23" t="s">
+      <c r="N5" t="s">
         <v>152</v>
       </c>
-      <c r="O5" s="23" t="s">
+      <c r="O5" t="s">
         <v>153</v>
       </c>
-      <c r="P5" s="23" t="s">
+      <c r="P5" t="s">
         <v>154</v>
       </c>
-      <c r="Q5" s="23" t="s">
+      <c r="Q5" t="s">
         <v>155</v>
       </c>
-      <c r="R5" s="23" t="s">
+      <c r="R5" t="s">
         <v>156</v>
       </c>
-      <c r="S5" s="23" t="s">
+      <c r="S5" t="s">
         <v>157</v>
       </c>
-      <c r="T5" s="23" t="s">
+      <c r="T5" t="s">
         <v>158</v>
       </c>
-      <c r="U5" s="23" t="s">
+      <c r="U5" t="s">
         <v>159</v>
       </c>
-      <c r="V5" s="23" t="s">
+      <c r="V5" t="s">
         <v>160</v>
       </c>
-      <c r="W5" s="23" t="s">
+      <c r="W5" t="s">
         <v>161</v>
       </c>
-      <c r="X5" s="23" t="s">
+      <c r="X5" t="s">
         <v>162</v>
       </c>
-      <c r="Y5" s="23" t="s">
+      <c r="Y5" t="s">
         <v>163</v>
       </c>
-      <c r="Z5" s="23" t="s">
+      <c r="Z5" t="s">
         <v>164</v>
       </c>
-      <c r="AA5" s="23" t="s">
+      <c r="AA5" t="s">
         <v>165</v>
       </c>
-      <c r="AB5" s="23" t="s">
+      <c r="AB5" t="s">
         <v>166</v>
       </c>
-      <c r="AC5" s="23" t="s">
+      <c r="AC5" t="s">
         <v>167</v>
       </c>
-      <c r="AD5" s="23" t="s">
+      <c r="AD5" t="s">
         <v>168</v>
       </c>
-      <c r="AE5" s="23" t="s">
+      <c r="AE5" t="s">
         <v>169</v>
       </c>
-      <c r="AF5" s="23" t="s">
+      <c r="AF5" t="s">
         <v>170</v>
       </c>
-      <c r="AG5" s="23" t="s">
+      <c r="AG5" t="s">
         <v>171</v>
       </c>
-      <c r="AH5" s="23" t="s">
+      <c r="AH5" t="s">
         <v>172</v>
       </c>
-      <c r="AI5" s="23" t="s">
+      <c r="AI5" t="s">
         <v>173</v>
       </c>
-      <c r="AJ5" s="23" t="s">
+      <c r="AJ5" t="s">
         <v>174</v>
       </c>
-      <c r="AK5" s="23" t="s">
+      <c r="AK5" t="s">
         <v>175</v>
       </c>
-      <c r="AL5" s="23" t="s">
+      <c r="AL5" t="s">
         <v>176</v>
       </c>
-      <c r="AM5" s="23" t="s">
+      <c r="AM5" t="s">
         <v>177</v>
       </c>
-      <c r="AN5" s="23" t="s">
+      <c r="AN5" t="s">
         <v>178</v>
       </c>
-      <c r="AO5" s="23" t="s">
+      <c r="AO5" t="s">
         <v>179</v>
       </c>
-      <c r="AP5" s="23" t="s">
+      <c r="AP5" t="s">
         <v>180</v>
       </c>
-      <c r="AQ5" s="23" t="s">
+      <c r="AQ5" t="s">
         <v>181</v>
       </c>
-      <c r="AR5" s="23" t="s">
+      <c r="AR5" t="s">
         <v>231</v>
       </c>
-      <c r="AS5" s="23" t="s">
+      <c r="AS5" t="s">
         <v>232</v>
       </c>
-      <c r="AT5" s="23" t="s">
+      <c r="AT5" t="s">
         <v>233</v>
       </c>
-      <c r="AU5" s="23" t="s">
+      <c r="AU5" t="s">
         <v>234</v>
       </c>
-      <c r="AV5" s="23" t="s">
+      <c r="AV5" t="s">
         <v>235</v>
       </c>
-      <c r="AW5" s="23" t="s">
+      <c r="AW5" t="s">
         <v>236</v>
       </c>
-      <c r="AX5" s="23" t="s">
+      <c r="AX5" t="s">
         <v>237</v>
       </c>
-      <c r="AY5" s="23" t="s">
+      <c r="AY5" t="s">
         <v>238</v>
       </c>
-      <c r="AZ5" s="23" t="s">
+      <c r="AZ5" t="s">
         <v>22</v>
       </c>
-      <c r="BA5" s="23" t="s">
+      <c r="BA5" t="s">
+        <v>730</v>
+      </c>
+      <c r="BB5" t="s">
         <v>731</v>
       </c>
-      <c r="BB5" s="23" t="s">
+      <c r="BC5" t="s">
         <v>732</v>
       </c>
-      <c r="BC5" s="23" t="s">
+      <c r="BD5" t="s">
         <v>733</v>
       </c>
-      <c r="BD5" s="23" t="s">
+      <c r="BE5" t="s">
         <v>734</v>
       </c>
-      <c r="BE5" s="23" t="s">
+      <c r="BF5" t="s">
         <v>735</v>
       </c>
-      <c r="BF5" s="23" t="s">
+      <c r="BG5" t="s">
         <v>736</v>
       </c>
-      <c r="BG5" s="23" t="s">
+      <c r="BH5" t="s">
         <v>737</v>
       </c>
-      <c r="BH5" s="23" t="s">
+      <c r="BI5" t="s">
         <v>738</v>
       </c>
-      <c r="BI5" s="23" t="s">
+      <c r="BJ5" t="s">
         <v>739</v>
       </c>
-      <c r="BJ5" s="23" t="s">
+      <c r="BK5" t="s">
         <v>740</v>
       </c>
-      <c r="BK5" s="23" t="s">
-        <v>741</v>
-      </c>
     </row>
-    <row r="6" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:63">
       <c r="B6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="23" t="s">
+      <c r="H6" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="I6" t="s">
         <v>112</v>
       </c>
-      <c r="J6" s="23" t="s">
+      <c r="J6" t="s">
         <v>115</v>
       </c>
-      <c r="K6" s="23" t="s">
+      <c r="K6" t="s">
         <v>182</v>
       </c>
-      <c r="L6" s="23" t="s">
+      <c r="L6" t="s">
         <v>183</v>
       </c>
-      <c r="M6" s="23" t="s">
+      <c r="M6" t="s">
         <v>184</v>
       </c>
-      <c r="N6" s="23" t="s">
+      <c r="N6" t="s">
         <v>185</v>
       </c>
-      <c r="O6" s="23" t="s">
+      <c r="O6" t="s">
         <v>186</v>
       </c>
-      <c r="P6" s="23" t="s">
+      <c r="P6" t="s">
         <v>187</v>
       </c>
-      <c r="Q6" s="23" t="s">
+      <c r="Q6" t="s">
         <v>188</v>
       </c>
-      <c r="R6" s="23" t="s">
+      <c r="R6" t="s">
         <v>189</v>
       </c>
-      <c r="S6" s="23" t="s">
+      <c r="S6" t="s">
         <v>190</v>
       </c>
-      <c r="T6" s="23" t="s">
+      <c r="T6" t="s">
         <v>191</v>
       </c>
-      <c r="U6" s="23" t="s">
+      <c r="U6" t="s">
         <v>192</v>
       </c>
-      <c r="V6" s="23" t="s">
+      <c r="V6" t="s">
         <v>193</v>
       </c>
-      <c r="W6" s="23" t="s">
+      <c r="W6" t="s">
         <v>194</v>
       </c>
-      <c r="X6" s="23" t="s">
+      <c r="X6" t="s">
         <v>195</v>
       </c>
-      <c r="Y6" s="23" t="s">
+      <c r="Y6" t="s">
         <v>196</v>
       </c>
-      <c r="Z6" s="23" t="s">
+      <c r="Z6" t="s">
         <v>197</v>
       </c>
-      <c r="AA6" s="23" t="s">
+      <c r="AA6" t="s">
         <v>198</v>
       </c>
-      <c r="AB6" s="23" t="s">
+      <c r="AB6" t="s">
         <v>199</v>
       </c>
-      <c r="AC6" s="23" t="s">
+      <c r="AC6" t="s">
         <v>200</v>
       </c>
-      <c r="AD6" s="23" t="s">
+      <c r="AD6" t="s">
         <v>201</v>
       </c>
-      <c r="AE6" s="23" t="s">
+      <c r="AE6" t="s">
         <v>202</v>
       </c>
-      <c r="AF6" s="23" t="s">
+      <c r="AF6" t="s">
         <v>203</v>
       </c>
-      <c r="AG6" s="23" t="s">
+      <c r="AG6" t="s">
         <v>204</v>
       </c>
-      <c r="AH6" s="23" t="s">
+      <c r="AH6" t="s">
         <v>205</v>
       </c>
-      <c r="AI6" s="23" t="s">
+      <c r="AI6" t="s">
         <v>206</v>
       </c>
-      <c r="AJ6" s="23" t="s">
+      <c r="AJ6" t="s">
         <v>207</v>
       </c>
-      <c r="AK6" s="23" t="s">
+      <c r="AK6" t="s">
         <v>208</v>
       </c>
-      <c r="AL6" s="23" t="s">
+      <c r="AL6" t="s">
         <v>209</v>
       </c>
-      <c r="AM6" s="23" t="s">
+      <c r="AM6" t="s">
         <v>210</v>
       </c>
-      <c r="AN6" s="23" t="s">
+      <c r="AN6" t="s">
         <v>211</v>
       </c>
-      <c r="AO6" s="23" t="s">
+      <c r="AO6" t="s">
         <v>212</v>
       </c>
-      <c r="AP6" s="23" t="s">
+      <c r="AP6" t="s">
         <v>213</v>
       </c>
-      <c r="AQ6" s="23" t="s">
+      <c r="AQ6" t="s">
         <v>214</v>
       </c>
-      <c r="AR6" s="23" t="s">
+      <c r="AR6" t="s">
         <v>239</v>
       </c>
-      <c r="AS6" s="23" t="s">
+      <c r="AS6" t="s">
         <v>240</v>
       </c>
-      <c r="AT6" s="23" t="s">
+      <c r="AT6" t="s">
         <v>241</v>
       </c>
-      <c r="AU6" s="23" t="s">
+      <c r="AU6" t="s">
         <v>242</v>
       </c>
-      <c r="AV6" s="23" t="s">
+      <c r="AV6" t="s">
         <v>243</v>
       </c>
-      <c r="AW6" s="23" t="s">
+      <c r="AW6" t="s">
         <v>244</v>
       </c>
-      <c r="AX6" s="23" t="s">
+      <c r="AX6" t="s">
         <v>245</v>
       </c>
-      <c r="AY6" s="23" t="s">
+      <c r="AY6" t="s">
         <v>246</v>
       </c>
-      <c r="AZ6" s="23" t="s">
+      <c r="AZ6" t="s">
         <v>32</v>
       </c>
-      <c r="BA6" s="23" t="s">
+      <c r="BA6" t="s">
+        <v>741</v>
+      </c>
+      <c r="BB6" t="s">
         <v>742</v>
       </c>
-      <c r="BB6" s="23" t="s">
+      <c r="BC6" t="s">
         <v>743</v>
       </c>
-      <c r="BC6" s="23" t="s">
+      <c r="BD6" t="s">
         <v>744</v>
       </c>
-      <c r="BD6" s="23" t="s">
+      <c r="BE6" t="s">
         <v>745</v>
       </c>
-      <c r="BE6" s="23" t="s">
+      <c r="BF6" t="s">
         <v>746</v>
       </c>
-      <c r="BF6" s="23" t="s">
+      <c r="BG6" t="s">
         <v>747</v>
       </c>
-      <c r="BG6" s="23" t="s">
+      <c r="BH6" t="s">
         <v>748</v>
       </c>
-      <c r="BH6" s="23" t="s">
+      <c r="BI6" t="s">
         <v>749</v>
       </c>
-      <c r="BI6" s="23" t="s">
+      <c r="BJ6" t="s">
         <v>750</v>
       </c>
-      <c r="BJ6" s="23" t="s">
+      <c r="BK6" t="s">
         <v>751</v>
       </c>
-      <c r="BK6" s="23" t="s">
-        <v>752</v>
-      </c>
     </row>
-    <row r="7" spans="2:63" x14ac:dyDescent="0.4">
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="23"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="23"/>
-      <c r="Y7" s="23"/>
-      <c r="Z7" s="23"/>
-      <c r="AA7" s="23"/>
-      <c r="AB7" s="23"/>
-      <c r="AC7" s="23"/>
-      <c r="AD7" s="23"/>
-      <c r="AE7" s="23"/>
-      <c r="AF7" s="23"/>
-      <c r="AG7" s="23"/>
-      <c r="AH7" s="23"/>
-      <c r="AI7" s="23"/>
-      <c r="AJ7" s="23"/>
-      <c r="AK7" s="23"/>
-      <c r="AL7" s="23"/>
-      <c r="AM7" s="23"/>
-      <c r="AN7" s="23"/>
-      <c r="AO7" s="23"/>
-      <c r="AP7" s="23"/>
-      <c r="AQ7" s="23"/>
-      <c r="AR7" s="23"/>
-      <c r="AS7" s="23"/>
-      <c r="AT7" s="23"/>
-      <c r="AU7" s="23"/>
-      <c r="AV7" s="23"/>
-      <c r="AW7" s="23"/>
-      <c r="AX7" s="23"/>
-      <c r="AY7" s="23"/>
-      <c r="AZ7" s="23"/>
-      <c r="BA7" s="23"/>
-      <c r="BB7" s="23"/>
-      <c r="BC7" s="23"/>
-      <c r="BD7" s="23"/>
-      <c r="BE7" s="23"/>
-      <c r="BF7" s="23"/>
-      <c r="BG7" s="23"/>
-      <c r="BH7" s="23"/>
-      <c r="BI7" s="23"/>
-      <c r="BJ7" s="23"/>
-      <c r="BK7" s="23"/>
-    </row>
-    <row r="8" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:63">
       <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="23"/>
-      <c r="W8" s="23"/>
-      <c r="X8" s="23"/>
-      <c r="Y8" s="23"/>
-      <c r="Z8" s="23"/>
-      <c r="AA8" s="23"/>
-      <c r="AB8" s="23"/>
-      <c r="AC8" s="23"/>
-      <c r="AD8" s="23"/>
-      <c r="AE8" s="23"/>
-      <c r="AF8" s="23"/>
-      <c r="AG8" s="23"/>
-      <c r="AH8" s="23"/>
-      <c r="AI8" s="23"/>
-      <c r="AJ8" s="23"/>
-      <c r="AK8" s="23"/>
-      <c r="AL8" s="23"/>
-      <c r="AM8" s="23"/>
-      <c r="AN8" s="23"/>
-      <c r="AO8" s="23"/>
-      <c r="AP8" s="23"/>
-      <c r="AQ8" s="23"/>
-      <c r="AR8" s="23"/>
-      <c r="AS8" s="23"/>
-      <c r="AT8" s="23"/>
-      <c r="AU8" s="23"/>
-      <c r="AV8" s="23"/>
-      <c r="AW8" s="23"/>
-      <c r="AX8" s="23"/>
-      <c r="AY8" s="23"/>
-      <c r="AZ8" s="23"/>
-      <c r="BA8" s="23"/>
-      <c r="BB8" s="23"/>
-      <c r="BC8" s="23"/>
-      <c r="BD8" s="23"/>
-      <c r="BE8" s="23"/>
-      <c r="BF8" s="23"/>
-      <c r="BG8" s="23"/>
-      <c r="BH8" s="23"/>
-      <c r="BI8" s="23"/>
-      <c r="BJ8" s="23"/>
-      <c r="BK8" s="23"/>
     </row>
-    <row r="9" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:63">
       <c r="B9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" t="s">
         <v>248</v>
       </c>
-      <c r="J9" s="23" t="s">
+      <c r="J9" t="s">
         <v>249</v>
       </c>
-      <c r="K9" s="23" t="s">
+      <c r="K9" t="s">
         <v>250</v>
       </c>
-      <c r="L9" s="23" t="s">
+      <c r="L9" t="s">
         <v>251</v>
       </c>
-      <c r="M9" s="23" t="s">
+      <c r="M9" t="s">
         <v>252</v>
       </c>
-      <c r="N9" s="23" t="s">
+      <c r="N9" t="s">
         <v>253</v>
       </c>
-      <c r="O9" s="23" t="s">
+      <c r="O9" t="s">
         <v>254</v>
       </c>
-      <c r="P9" s="23" t="s">
+      <c r="P9" t="s">
         <v>255</v>
       </c>
-      <c r="Q9" s="23" t="s">
+      <c r="Q9" t="s">
         <v>256</v>
       </c>
-      <c r="R9" s="23" t="s">
+      <c r="R9" t="s">
         <v>257</v>
       </c>
-      <c r="S9" s="23" t="s">
+      <c r="S9" t="s">
         <v>258</v>
       </c>
-      <c r="T9" s="23" t="s">
+      <c r="T9" t="s">
         <v>259</v>
       </c>
-      <c r="U9" s="23" t="s">
+      <c r="U9" t="s">
         <v>260</v>
       </c>
-      <c r="V9" s="23" t="s">
+      <c r="V9" t="s">
         <v>261</v>
       </c>
-      <c r="W9" s="23" t="s">
+      <c r="W9" t="s">
         <v>262</v>
       </c>
-      <c r="X9" s="23" t="s">
+      <c r="X9" t="s">
         <v>263</v>
       </c>
-      <c r="Y9" s="23" t="s">
+      <c r="Y9" t="s">
         <v>264</v>
       </c>
-      <c r="Z9" s="23" t="s">
+      <c r="Z9" t="s">
         <v>265</v>
       </c>
-      <c r="AA9" s="23" t="s">
+      <c r="AA9" t="s">
         <v>266</v>
       </c>
-      <c r="AB9" s="23" t="s">
+      <c r="AB9" t="s">
         <v>267</v>
       </c>
-      <c r="AC9" s="23" t="s">
+      <c r="AC9" t="s">
         <v>268</v>
       </c>
-      <c r="AD9" s="23" t="s">
+      <c r="AD9" t="s">
         <v>269</v>
       </c>
-      <c r="AE9" s="23" t="s">
+      <c r="AE9" t="s">
         <v>270</v>
       </c>
-      <c r="AF9" s="23" t="s">
+      <c r="AF9" t="s">
         <v>271</v>
       </c>
-      <c r="AG9" s="23" t="s">
+      <c r="AG9" t="s">
         <v>272</v>
       </c>
-      <c r="AH9" s="23" t="s">
+      <c r="AH9" t="s">
         <v>273</v>
       </c>
-      <c r="AI9" s="23" t="s">
+      <c r="AI9" t="s">
         <v>274</v>
       </c>
-      <c r="AJ9" s="23" t="s">
+      <c r="AJ9" t="s">
         <v>275</v>
       </c>
-      <c r="AK9" s="23" t="s">
+      <c r="AK9" t="s">
         <v>276</v>
       </c>
-      <c r="AL9" s="23" t="s">
+      <c r="AL9" t="s">
         <v>277</v>
       </c>
-      <c r="AM9" s="23" t="s">
+      <c r="AM9" t="s">
         <v>278</v>
       </c>
-      <c r="AN9" s="23" t="s">
+      <c r="AN9" t="s">
         <v>279</v>
       </c>
-      <c r="AO9" s="23" t="s">
+      <c r="AO9" t="s">
         <v>280</v>
       </c>
-      <c r="AP9" s="23" t="s">
+      <c r="AP9" t="s">
         <v>281</v>
       </c>
-      <c r="AQ9" s="23" t="s">
+      <c r="AQ9" t="s">
         <v>282</v>
       </c>
-      <c r="AR9" s="23" t="s">
+      <c r="AR9" t="s">
         <v>283</v>
       </c>
-      <c r="AS9" s="23" t="s">
+      <c r="AS9" t="s">
         <v>284</v>
       </c>
-      <c r="AT9" s="23" t="s">
+      <c r="AT9" t="s">
         <v>285</v>
       </c>
-      <c r="AU9" s="23" t="s">
+      <c r="AU9" t="s">
         <v>286</v>
       </c>
-      <c r="AV9" s="23" t="s">
+      <c r="AV9" t="s">
         <v>287</v>
       </c>
-      <c r="AW9" s="23" t="s">
+      <c r="AW9" t="s">
         <v>288</v>
       </c>
-      <c r="AX9" s="23" t="s">
+      <c r="AX9" t="s">
         <v>289</v>
       </c>
-      <c r="AY9" s="23" t="s">
+      <c r="AY9" t="s">
         <v>290</v>
       </c>
-      <c r="AZ9" s="23" t="s">
+      <c r="AZ9" t="s">
         <v>291</v>
       </c>
-      <c r="BA9" s="23" t="s">
+      <c r="BA9" t="s">
+        <v>653</v>
+      </c>
+      <c r="BB9" t="s">
         <v>654</v>
       </c>
-      <c r="BB9" s="23" t="s">
+      <c r="BC9" t="s">
         <v>655</v>
       </c>
-      <c r="BC9" s="23" t="s">
+      <c r="BD9" t="s">
         <v>656</v>
       </c>
-      <c r="BD9" s="23" t="s">
+      <c r="BE9" t="s">
         <v>657</v>
       </c>
-      <c r="BE9" s="23" t="s">
+      <c r="BF9" t="s">
         <v>658</v>
       </c>
-      <c r="BF9" s="23" t="s">
+      <c r="BG9" t="s">
         <v>659</v>
       </c>
-      <c r="BG9" s="23" t="s">
+      <c r="BH9" t="s">
         <v>660</v>
       </c>
-      <c r="BH9" s="23" t="s">
+      <c r="BI9" t="s">
         <v>661</v>
       </c>
-      <c r="BI9" s="23" t="s">
+      <c r="BJ9" t="s">
         <v>662</v>
       </c>
-      <c r="BJ9" s="23" t="s">
+      <c r="BK9" t="s">
         <v>663</v>
       </c>
-      <c r="BK9" s="23" t="s">
-        <v>664</v>
-      </c>
     </row>
-    <row r="10" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:63">
       <c r="B10" s="1"/>
       <c r="C10" t="s">
         <v>3</v>
@@ -7374,7 +7403,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:63">
       <c r="B11" s="2"/>
       <c r="C11" t="s">
         <v>43</v>
@@ -7527,43 +7556,43 @@
         <v>335</v>
       </c>
       <c r="BA11" t="s">
+        <v>664</v>
+      </c>
+      <c r="BB11" t="s">
         <v>665</v>
       </c>
-      <c r="BB11" t="s">
+      <c r="BC11" t="s">
         <v>666</v>
       </c>
-      <c r="BC11" t="s">
+      <c r="BD11" t="s">
         <v>667</v>
       </c>
-      <c r="BD11" t="s">
+      <c r="BE11" t="s">
         <v>668</v>
       </c>
-      <c r="BE11" t="s">
+      <c r="BF11" t="s">
         <v>669</v>
       </c>
-      <c r="BF11" t="s">
+      <c r="BG11" t="s">
         <v>670</v>
       </c>
-      <c r="BG11" t="s">
+      <c r="BH11" t="s">
         <v>671</v>
       </c>
-      <c r="BH11" t="s">
+      <c r="BI11" t="s">
         <v>672</v>
       </c>
-      <c r="BI11" t="s">
+      <c r="BJ11" t="s">
         <v>673</v>
       </c>
-      <c r="BJ11" t="s">
+      <c r="BK11" t="s">
         <v>674</v>
       </c>
-      <c r="BK11" t="s">
-        <v>675</v>
-      </c>
     </row>
-    <row r="12" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:63">
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:63">
       <c r="B13" s="2">
         <v>0.16666666666666666</v>
       </c>
@@ -7718,40 +7747,40 @@
         <v>379</v>
       </c>
       <c r="BA13" t="s">
+        <v>675</v>
+      </c>
+      <c r="BB13" t="s">
         <v>676</v>
       </c>
-      <c r="BB13" t="s">
+      <c r="BC13" t="s">
         <v>677</v>
       </c>
-      <c r="BC13" t="s">
+      <c r="BD13" t="s">
         <v>678</v>
       </c>
-      <c r="BD13" t="s">
+      <c r="BE13" t="s">
         <v>679</v>
       </c>
-      <c r="BE13" t="s">
+      <c r="BF13" t="s">
         <v>680</v>
       </c>
-      <c r="BF13" t="s">
+      <c r="BG13" t="s">
         <v>681</v>
       </c>
-      <c r="BG13" t="s">
+      <c r="BH13" t="s">
         <v>682</v>
       </c>
-      <c r="BH13" t="s">
+      <c r="BI13" t="s">
         <v>683</v>
       </c>
-      <c r="BI13" t="s">
+      <c r="BJ13" t="s">
         <v>684</v>
       </c>
-      <c r="BJ13" t="s">
+      <c r="BK13" t="s">
         <v>685</v>
       </c>
-      <c r="BK13" t="s">
-        <v>686</v>
-      </c>
     </row>
-    <row r="14" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:63">
       <c r="B14" s="1" t="s">
         <v>3</v>
       </c>
@@ -7939,7 +7968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:63">
       <c r="B15" s="2">
         <v>0.99930555555555556</v>
       </c>
@@ -8094,40 +8123,40 @@
         <v>473</v>
       </c>
       <c r="BA15" t="s">
+        <v>686</v>
+      </c>
+      <c r="BB15" t="s">
         <v>687</v>
       </c>
-      <c r="BB15" t="s">
+      <c r="BC15" t="s">
         <v>688</v>
       </c>
-      <c r="BC15" t="s">
+      <c r="BD15" t="s">
         <v>689</v>
       </c>
-      <c r="BD15" t="s">
+      <c r="BE15" t="s">
         <v>690</v>
       </c>
-      <c r="BE15" t="s">
+      <c r="BF15" t="s">
         <v>691</v>
       </c>
-      <c r="BF15" t="s">
+      <c r="BG15" t="s">
         <v>692</v>
       </c>
-      <c r="BG15" t="s">
+      <c r="BH15" t="s">
         <v>693</v>
       </c>
-      <c r="BH15" t="s">
+      <c r="BI15" t="s">
         <v>694</v>
       </c>
-      <c r="BI15" t="s">
+      <c r="BJ15" t="s">
         <v>695</v>
       </c>
-      <c r="BJ15" t="s">
+      <c r="BK15" t="s">
         <v>696</v>
       </c>
-      <c r="BK15" t="s">
-        <v>697</v>
-      </c>
     </row>
-    <row r="16" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:63">
       <c r="B16" s="2">
         <v>0</v>
       </c>
@@ -8282,40 +8311,40 @@
         <v>523</v>
       </c>
       <c r="BA16" t="s">
+        <v>697</v>
+      </c>
+      <c r="BB16" t="s">
         <v>698</v>
       </c>
-      <c r="BB16" t="s">
+      <c r="BC16" t="s">
         <v>699</v>
       </c>
-      <c r="BC16" t="s">
+      <c r="BD16" t="s">
         <v>700</v>
       </c>
-      <c r="BD16" t="s">
+      <c r="BE16" t="s">
         <v>701</v>
       </c>
-      <c r="BE16" t="s">
+      <c r="BF16" t="s">
         <v>702</v>
       </c>
-      <c r="BF16" t="s">
+      <c r="BG16" t="s">
         <v>703</v>
       </c>
-      <c r="BG16" t="s">
+      <c r="BH16" t="s">
         <v>704</v>
       </c>
-      <c r="BH16" t="s">
+      <c r="BI16" t="s">
         <v>705</v>
       </c>
-      <c r="BI16" t="s">
+      <c r="BJ16" t="s">
         <v>706</v>
       </c>
-      <c r="BJ16" t="s">
+      <c r="BK16" t="s">
         <v>707</v>
       </c>
-      <c r="BK16" t="s">
-        <v>708</v>
-      </c>
     </row>
-    <row r="17" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:63">
       <c r="B17" s="1" t="s">
         <v>3</v>
       </c>
@@ -8503,7 +8532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:63">
       <c r="B18" s="2">
         <v>0.16597222222222222</v>
       </c>
@@ -8658,47 +8687,47 @@
         <v>423</v>
       </c>
       <c r="BA18" t="s">
+        <v>708</v>
+      </c>
+      <c r="BB18" t="s">
         <v>709</v>
       </c>
-      <c r="BB18" t="s">
+      <c r="BC18" t="s">
         <v>710</v>
       </c>
-      <c r="BC18" t="s">
+      <c r="BD18" t="s">
         <v>711</v>
       </c>
-      <c r="BD18" t="s">
+      <c r="BE18" t="s">
         <v>712</v>
       </c>
-      <c r="BE18" t="s">
+      <c r="BF18" t="s">
         <v>713</v>
       </c>
-      <c r="BF18" t="s">
+      <c r="BG18" t="s">
         <v>714</v>
       </c>
-      <c r="BG18" t="s">
+      <c r="BH18" t="s">
         <v>715</v>
       </c>
-      <c r="BH18" t="s">
+      <c r="BI18" t="s">
         <v>716</v>
       </c>
-      <c r="BI18" t="s">
+      <c r="BJ18" t="s">
         <v>717</v>
       </c>
-      <c r="BJ18" t="s">
+      <c r="BK18" t="s">
         <v>718</v>
       </c>
-      <c r="BK18" t="s">
-        <v>719</v>
-      </c>
     </row>
-    <row r="20" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:63">
       <c r="B20" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="14"/>
     </row>
-    <row r="21" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:63">
       <c r="B21" s="11" t="s">
         <v>55</v>
       </c>
@@ -8709,7 +8738,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="22" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:63">
       <c r="B22" s="11" t="s">
         <v>56</v>
       </c>
@@ -8720,7 +8749,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="23" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:63">
       <c r="B23" s="7" t="s">
         <v>57</v>
       </c>
@@ -8731,7 +8760,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="24" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:63">
       <c r="B24" s="7" t="s">
         <v>58</v>
       </c>
@@ -8742,7 +8771,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="25" spans="2:63" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:63">
       <c r="B25" s="7" t="s">
         <v>59</v>
       </c>
@@ -8753,7 +8782,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="26" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:63" s="5" customFormat="1">
       <c r="B26" s="8" t="s">
         <v>60</v>
       </c>
@@ -8764,7 +8793,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="27" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:63" s="5" customFormat="1">
       <c r="B27" s="12" t="s">
         <v>61</v>
       </c>
@@ -8775,7 +8804,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="28" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:63" s="5" customFormat="1">
       <c r="B28" s="8" t="s">
         <v>62</v>
       </c>
@@ -8786,23 +8815,23 @@
         <v>567</v>
       </c>
     </row>
-    <row r="29" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:63" s="5" customFormat="1">
       <c r="B29" t="s">
         <v>39</v>
       </c>
       <c r="C29" s="6"/>
     </row>
-    <row r="30" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:63" s="5" customFormat="1">
       <c r="B30" t="s">
         <v>25</v>
       </c>
       <c r="C30" s="6"/>
     </row>
-    <row r="31" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:63" s="5" customFormat="1">
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
     </row>
-    <row r="32" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:63" s="5" customFormat="1">
       <c r="B32" s="6" t="s">
         <v>63</v>
       </c>
@@ -8811,9 +8840,10 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" verticalDpi="1200" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/docs/光和稼働データ収集装置デバイスマップ.xlsx
+++ b/docs/光和稼働データ収集装置デバイスマップ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877E1234-4109-4527-BC61-341CBBEEFEE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C5B5BC-A60A-4B3E-94D9-0C361B398E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{2B542973-F752-4A81-A420-BFC37E5D0A51}"/>
   </bookViews>
@@ -23,136 +23,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>user</author>
-  </authors>
-  <commentList>
-    <comment ref="AC1" authorId="0" shapeId="0" xr:uid="{DD7276A9-1BA8-4376-A68B-8B46A03145DC}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="ＭＳ Ｐゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">タッチパネルデータでは
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="2"/>
-            <charset val="128"/>
-          </rPr>
-          <t>DM436</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="ＭＳ Ｐゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">を使用している
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="2"/>
-            <charset val="128"/>
-          </rPr>
-          <t>(規則性が崩れている)</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="ＭＳ Ｐゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">
-生産数実績</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="2"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">=DM536
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="ＭＳ Ｐゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>生産数目標</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="2"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">=DM636
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="ＭＳ Ｐゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t>アラーム数</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="MS P ゴシック"/>
-            <family val="2"/>
-            <charset val="128"/>
-          </rPr>
-          <t>=DM736</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="ＭＳ Ｐゴシック"/>
-            <family val="3"/>
-            <charset val="128"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2698,7 +2568,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2756,22 +2626,8 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="MS P ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2823,12 +2679,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF66CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF99CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2945,7 +2795,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3439,13 +3289,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62123ED-9C66-404D-AD1C-3CC6E3D9A234}">
   <dimension ref="B1:AZ32"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
     <col min="3" max="52" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:52">
+    <row r="1" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
         <v>570</v>
       </c>
@@ -3600,7 +3450,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="2" spans="2:52">
+    <row r="2" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
         <v>38</v>
       </c>
@@ -3755,7 +3605,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="3" spans="2:52">
+    <row r="3" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>66</v>
       </c>
@@ -3896,7 +3746,7 @@
       <c r="AY3" s="10"/>
       <c r="AZ3" s="10"/>
     </row>
-    <row r="4" spans="2:52">
+    <row r="4" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
@@ -4051,7 +3901,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="2:52">
+    <row r="5" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
@@ -4206,7 +4056,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="2:52">
+    <row r="6" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B6" s="1" t="s">
         <v>24</v>
       </c>
@@ -4361,12 +4211,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="2:52">
+    <row r="8" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="2:52">
+    <row r="9" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B9" s="2" t="s">
         <v>52</v>
       </c>
@@ -4521,7 +4371,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="10" spans="2:52">
+    <row r="10" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B10" s="1"/>
       <c r="C10" t="s">
         <v>3</v>
@@ -4674,7 +4524,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="2:52">
+    <row r="11" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B11" s="2"/>
       <c r="C11" t="s">
         <v>43</v>
@@ -4827,10 +4677,10 @@
         <v>335</v>
       </c>
     </row>
-    <row r="12" spans="2:52">
+    <row r="12" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="2:52">
+    <row r="13" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B13" s="2">
         <v>0.16666666666666666</v>
       </c>
@@ -4985,7 +4835,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="14" spans="2:52">
+    <row r="14" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B14" s="1" t="s">
         <v>3</v>
       </c>
@@ -5140,7 +4990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="2:52">
+    <row r="15" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B15" s="2">
         <v>0.99930555555555556</v>
       </c>
@@ -5295,7 +5145,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="16" spans="2:52">
+    <row r="16" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B16" s="2">
         <v>0</v>
       </c>
@@ -5450,7 +5300,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="17" spans="2:52">
+    <row r="17" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B17" s="1" t="s">
         <v>3</v>
       </c>
@@ -5605,7 +5455,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:52">
+    <row r="18" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B18" s="2">
         <v>0.16597222222222222</v>
       </c>
@@ -5760,14 +5610,14 @@
         <v>423</v>
       </c>
     </row>
-    <row r="20" spans="2:52">
+    <row r="20" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B20" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="14"/>
     </row>
-    <row r="21" spans="2:52">
+    <row r="21" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B21" s="11" t="s">
         <v>55</v>
       </c>
@@ -5778,7 +5628,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="22" spans="2:52">
+    <row r="22" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B22" s="11" t="s">
         <v>56</v>
       </c>
@@ -5789,7 +5639,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="23" spans="2:52">
+    <row r="23" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B23" s="7" t="s">
         <v>57</v>
       </c>
@@ -5800,7 +5650,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="24" spans="2:52">
+    <row r="24" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B24" s="7" t="s">
         <v>58</v>
       </c>
@@ -5811,7 +5661,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="25" spans="2:52">
+    <row r="25" spans="2:52" x14ac:dyDescent="0.4">
       <c r="B25" s="7" t="s">
         <v>59</v>
       </c>
@@ -5822,7 +5672,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="26" spans="2:52" s="5" customFormat="1">
+    <row r="26" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B26" s="8" t="s">
         <v>60</v>
       </c>
@@ -5833,7 +5683,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="27" spans="2:52" s="5" customFormat="1">
+    <row r="27" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B27" s="12" t="s">
         <v>61</v>
       </c>
@@ -5844,7 +5694,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="28" spans="2:52" s="5" customFormat="1">
+    <row r="28" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B28" s="8" t="s">
         <v>62</v>
       </c>
@@ -5855,23 +5705,23 @@
         <v>567</v>
       </c>
     </row>
-    <row r="29" spans="2:52" s="5" customFormat="1">
+    <row r="29" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B29" t="s">
         <v>39</v>
       </c>
       <c r="C29" s="6"/>
     </row>
-    <row r="30" spans="2:52" s="5" customFormat="1">
+    <row r="30" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B30" t="s">
         <v>25</v>
       </c>
       <c r="C30" s="6"/>
     </row>
-    <row r="31" spans="2:52" s="5" customFormat="1">
+    <row r="31" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
     </row>
-    <row r="32" spans="2:52" s="5" customFormat="1">
+    <row r="32" spans="2:52" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B32" s="6" t="s">
         <v>63</v>
       </c>
@@ -5888,15 +5738,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65309343-5134-42B2-91CD-0F008F8E70CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65309343-5134-42B2-91CD-0F008F8E70CA}">
   <dimension ref="B1:BK32"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
     <col min="3" max="52" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:63">
+    <row r="1" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B1" s="22" t="s">
         <v>570</v>
       </c>
@@ -6084,7 +5934,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="2" spans="2:63">
+    <row r="2" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B2" s="4" t="s">
         <v>38</v>
       </c>
@@ -6272,7 +6122,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="3" spans="2:63">
+    <row r="3" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B3" s="4" t="s">
         <v>66</v>
       </c>
@@ -6460,7 +6310,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="4" spans="2:63">
+    <row r="4" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
@@ -6648,7 +6498,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="5" spans="2:63">
+    <row r="5" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
@@ -6836,7 +6686,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="6" spans="2:63">
+    <row r="6" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B6" s="1" t="s">
         <v>24</v>
       </c>
@@ -7024,12 +6874,12 @@
         <v>751</v>
       </c>
     </row>
-    <row r="8" spans="2:63">
+    <row r="8" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B8" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="2:63">
+    <row r="9" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B9" s="2" t="s">
         <v>52</v>
       </c>
@@ -7217,7 +7067,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="10" spans="2:63">
+    <row r="10" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B10" s="1"/>
       <c r="C10" t="s">
         <v>3</v>
@@ -7403,7 +7253,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="2:63">
+    <row r="11" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B11" s="2"/>
       <c r="C11" t="s">
         <v>43</v>
@@ -7589,10 +7439,10 @@
         <v>674</v>
       </c>
     </row>
-    <row r="12" spans="2:63">
+    <row r="12" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B12" s="2"/>
     </row>
-    <row r="13" spans="2:63">
+    <row r="13" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B13" s="2">
         <v>0.16666666666666666</v>
       </c>
@@ -7780,7 +7630,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="14" spans="2:63">
+    <row r="14" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B14" s="1" t="s">
         <v>3</v>
       </c>
@@ -7968,7 +7818,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="2:63">
+    <row r="15" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B15" s="2">
         <v>0.99930555555555556</v>
       </c>
@@ -8156,7 +8006,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="16" spans="2:63">
+    <row r="16" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B16" s="2">
         <v>0</v>
       </c>
@@ -8344,7 +8194,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="17" spans="2:63">
+    <row r="17" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B17" s="1" t="s">
         <v>3</v>
       </c>
@@ -8532,7 +8382,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:63">
+    <row r="18" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B18" s="2">
         <v>0.16597222222222222</v>
       </c>
@@ -8720,14 +8570,14 @@
         <v>718</v>
       </c>
     </row>
-    <row r="20" spans="2:63">
+    <row r="20" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B20" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="14"/>
     </row>
-    <row r="21" spans="2:63">
+    <row r="21" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B21" s="11" t="s">
         <v>55</v>
       </c>
@@ -8738,7 +8588,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="22" spans="2:63">
+    <row r="22" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B22" s="11" t="s">
         <v>56</v>
       </c>
@@ -8749,7 +8599,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="23" spans="2:63">
+    <row r="23" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B23" s="7" t="s">
         <v>57</v>
       </c>
@@ -8760,7 +8610,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="24" spans="2:63">
+    <row r="24" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B24" s="7" t="s">
         <v>58</v>
       </c>
@@ -8771,7 +8621,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="25" spans="2:63">
+    <row r="25" spans="2:63" x14ac:dyDescent="0.4">
       <c r="B25" s="7" t="s">
         <v>59</v>
       </c>
@@ -8782,7 +8632,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="26" spans="2:63" s="5" customFormat="1">
+    <row r="26" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B26" s="8" t="s">
         <v>60</v>
       </c>
@@ -8793,7 +8643,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="27" spans="2:63" s="5" customFormat="1">
+    <row r="27" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B27" s="12" t="s">
         <v>61</v>
       </c>
@@ -8804,7 +8654,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="28" spans="2:63" s="5" customFormat="1">
+    <row r="28" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B28" s="8" t="s">
         <v>62</v>
       </c>
@@ -8815,23 +8665,23 @@
         <v>567</v>
       </c>
     </row>
-    <row r="29" spans="2:63" s="5" customFormat="1">
+    <row r="29" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B29" t="s">
         <v>39</v>
       </c>
       <c r="C29" s="6"/>
     </row>
-    <row r="30" spans="2:63" s="5" customFormat="1">
+    <row r="30" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B30" t="s">
         <v>25</v>
       </c>
       <c r="C30" s="6"/>
     </row>
-    <row r="31" spans="2:63" s="5" customFormat="1">
+    <row r="31" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
     </row>
-    <row r="32" spans="2:63" s="5" customFormat="1">
+    <row r="32" spans="2:63" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="B32" s="6" t="s">
         <v>63</v>
       </c>
@@ -8841,9 +8691,8 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="1200" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>